--- a/data/trans_camb/IP15-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP15-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 6,57</t>
+          <t>-10,43; 7,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 2,73</t>
+          <t>-13,64; 2,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 7,39</t>
+          <t>-10,06; 7,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 11,04</t>
+          <t>-4,15; 11,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 4,79</t>
+          <t>-10,0; 5,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 9,08</t>
+          <t>-7,22; 9,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 6,97</t>
+          <t>-4,11; 7,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 1,55</t>
+          <t>-9,33; 1,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 5,91</t>
+          <t>-6,9; 5,84</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,21; 35,66</t>
+          <t>-35,74; 35,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,23; 17,17</t>
+          <t>-50,29; 12,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,08; 35,43</t>
+          <t>-37,74; 37,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 73,94</t>
+          <t>-18,59; 77,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,22; 31,59</t>
+          <t>-43,95; 36,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,3; 57,72</t>
+          <t>-33,93; 56,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 38,95</t>
+          <t>-17,8; 40,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 8,57</t>
+          <t>-40,01; 9,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-24,82; 32,29</t>
+          <t>-28,33; 30,92</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 4,72</t>
+          <t>-7,94; 4,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 5,79</t>
+          <t>-6,94; 5,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 11,14</t>
+          <t>-5,35; 10,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 4,61</t>
+          <t>-7,58; 4,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 4,04</t>
+          <t>-7,05; 4,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 12,59</t>
+          <t>-0,71; 12,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 2,86</t>
+          <t>-5,89; 3,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 3,48</t>
+          <t>-5,56; 2,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 9,41</t>
+          <t>-0,26; 9,84</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,42; 26,62</t>
+          <t>-32,17; 26,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,39; 31,76</t>
+          <t>-30,01; 31,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 60,26</t>
+          <t>-22,63; 56,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,41; 28,15</t>
+          <t>-33,28; 28,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,41; 24,28</t>
+          <t>-31,26; 30,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 77,01</t>
+          <t>-3,76; 75,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,44; 15,76</t>
+          <t>-26,07; 17,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 18,43</t>
+          <t>-24,48; 15,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 51,14</t>
+          <t>-1,38; 52,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 10,02</t>
+          <t>-3,83; 10,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 6,26</t>
+          <t>-7,76; 5,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,17; 49,93</t>
+          <t>10,26; 46,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 5,93</t>
+          <t>-8,91; 5,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 0,52</t>
+          <t>-13,68; 0,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 15,95</t>
+          <t>-1,21; 16,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 5,96</t>
+          <t>-4,36; 6,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 1,02</t>
+          <t>-9,2; 0,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,06; 30,92</t>
+          <t>7,98; 31,55</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 68,32</t>
+          <t>-19,12; 70,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,78; 43,09</t>
+          <t>-34,31; 37,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49,52; 352,75</t>
+          <t>45,58; 315,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,24; 31,03</t>
+          <t>-32,44; 28,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,84; 3,9</t>
+          <t>-50,13; 2,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 83,41</t>
+          <t>-4,9; 86,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 33,13</t>
+          <t>-18,79; 34,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,0; 5,01</t>
+          <t>-37,71; 4,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,98; 153,45</t>
+          <t>33,75; 158,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 13,5</t>
+          <t>1,6; 13,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 9,49</t>
+          <t>-2,54; 9,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 11,52</t>
+          <t>0,11; 11,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 10,84</t>
+          <t>-2,27; 11,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 2,73</t>
+          <t>-10,78; 1,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 6,84</t>
+          <t>-6,73; 6,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 10,05</t>
+          <t>1,24; 10,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 4,1</t>
+          <t>-4,41; 3,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 7,24</t>
+          <t>-1,41; 8,03</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,62; 140,62</t>
+          <t>10,15; 148,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 103,56</t>
+          <t>-18,06; 100,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 114,67</t>
+          <t>-0,74; 123,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 73,4</t>
+          <t>-11,38; 70,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-45,76; 16,6</t>
+          <t>-47,81; 11,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,96; 44,28</t>
+          <t>-31,78; 43,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,68; 74,59</t>
+          <t>6,89; 77,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 30,84</t>
+          <t>-24,62; 27,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 54,61</t>
+          <t>-8,33; 60,94</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 6,0</t>
+          <t>-1,19; 5,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 2,73</t>
+          <t>-3,52; 2,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,55; 18,68</t>
+          <t>3,37; 19,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 4,37</t>
+          <t>-2,47; 4,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,64; -0,23</t>
+          <t>-6,91; -0,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 7,6</t>
+          <t>0,53; 7,5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 4,24</t>
+          <t>-0,96; 4,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,37</t>
+          <t>-4,44; 0,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,2; 11,67</t>
+          <t>3,11; 11,58</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 35,93</t>
+          <t>-6,23; 33,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 16,14</t>
+          <t>-18,08; 16,95</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17,95; 107,36</t>
+          <t>17,42; 112,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 23,94</t>
+          <t>-11,14; 24,47</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-30,26; -1,01</t>
+          <t>-31,19; -0,16</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 41,43</t>
+          <t>2,39; 41,04</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 23,55</t>
+          <t>-4,67; 22,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 2,04</t>
+          <t>-21,34; 1,47</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15,68; 61,83</t>
+          <t>15,21; 62,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP15-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP15-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 7,06</t>
+          <t>-9,5; 7,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 2,56</t>
+          <t>-14,31; 2,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 7,36</t>
+          <t>-9,99; 7,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 11,52</t>
+          <t>-3,51; 11,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 5,17</t>
+          <t>-9,13; 5,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 9,34</t>
+          <t>-6,55; 10,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 7,46</t>
+          <t>-3,78; 6,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 1,93</t>
+          <t>-9,25; 1,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 5,84</t>
+          <t>-5,66; 6,53</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,74; 35,85</t>
+          <t>-34,57; 40,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,29; 12,38</t>
+          <t>-50,75; 16,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-37,74; 37,54</t>
+          <t>-35,7; 38,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 77,03</t>
+          <t>-16,97; 77,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,95; 36,07</t>
+          <t>-41,39; 37,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,93; 56,56</t>
+          <t>-31,67; 70,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 40,22</t>
+          <t>-16,22; 37,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 9,81</t>
+          <t>-38,67; 8,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-28,33; 30,92</t>
+          <t>-23,93; 36,29</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 4,95</t>
+          <t>-7,31; 4,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 5,42</t>
+          <t>-6,94; 5,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 10,39</t>
+          <t>-5,09; 11,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 4,74</t>
+          <t>-8,33; 4,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 4,82</t>
+          <t>-7,77; 4,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 12,4</t>
+          <t>-0,79; 12,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 3,14</t>
+          <t>-6,03; 3,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 2,8</t>
+          <t>-5,42; 3,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 9,84</t>
+          <t>-0,97; 8,89</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,17; 26,24</t>
+          <t>-29,31; 25,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,01; 31,2</t>
+          <t>-28,23; 32,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,63; 56,92</t>
+          <t>-22,34; 60,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,28; 28,44</t>
+          <t>-35,42; 26,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,26; 30,46</t>
+          <t>-33,6; 29,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 75,93</t>
+          <t>-4,4; 72,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,07; 17,34</t>
+          <t>-26,85; 17,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,48; 15,49</t>
+          <t>-23,86; 16,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 52,44</t>
+          <t>-4,33; 50,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 10,58</t>
+          <t>-4,1; 9,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 5,56</t>
+          <t>-7,6; 6,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,26; 46,84</t>
+          <t>10,78; 46,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 5,63</t>
+          <t>-8,02; 6,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 0,26</t>
+          <t>-14,1; 0,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 16,61</t>
+          <t>-1,09; 16,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 6,39</t>
+          <t>-4,5; 6,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 0,85</t>
+          <t>-9,05; 1,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,98; 31,55</t>
+          <t>7,89; 29,3</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 70,5</t>
+          <t>-19,43; 63,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,31; 37,43</t>
+          <t>-34,9; 46,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45,58; 315,87</t>
+          <t>52,02; 331,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,44; 28,7</t>
+          <t>-30,05; 34,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,13; 2,66</t>
+          <t>-50,75; 6,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 86,78</t>
+          <t>-4,21; 80,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 34,95</t>
+          <t>-19,16; 33,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,71; 4,83</t>
+          <t>-38,7; 6,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33,75; 158,78</t>
+          <t>32,83; 150,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 13,78</t>
+          <t>1,64; 14,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 9,63</t>
+          <t>-2,37; 9,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 11,81</t>
+          <t>0,23; 12,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 11,03</t>
+          <t>-2,11; 10,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 1,77</t>
+          <t>-10,61; 2,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 6,58</t>
+          <t>-6,17; 6,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 10,3</t>
+          <t>1,39; 10,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 3,76</t>
+          <t>-4,16; 4,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 8,03</t>
+          <t>-1,64; 7,8</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,15; 148,24</t>
+          <t>10,41; 154,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 100,26</t>
+          <t>-14,65; 103,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 123,38</t>
+          <t>-0,5; 126,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 70,69</t>
+          <t>-10,11; 70,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,81; 11,3</t>
+          <t>-48,81; 14,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-31,78; 43,44</t>
+          <t>-28,1; 45,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,89; 77,24</t>
+          <t>7,5; 77,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,62; 27,97</t>
+          <t>-23,71; 33,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 60,94</t>
+          <t>-9,36; 59,13</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 5,73</t>
+          <t>-1,29; 5,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 2,82</t>
+          <t>-3,86; 2,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,37; 19,5</t>
+          <t>3,24; 18,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 4,39</t>
+          <t>-2,18; 4,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,91; -0,09</t>
+          <t>-6,66; -0,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,53; 7,5</t>
+          <t>0,37; 8,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,02</t>
+          <t>-0,58; 4,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,25</t>
+          <t>-4,04; 0,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,11; 11,58</t>
+          <t>3,17; 10,59</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 33,43</t>
+          <t>-6,72; 34,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 16,95</t>
+          <t>-19,63; 15,96</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17,42; 112,51</t>
+          <t>16,31; 104,05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 24,47</t>
+          <t>-10,22; 25,21</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-31,19; -0,16</t>
+          <t>-30,25; -0,48</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,39; 41,04</t>
+          <t>1,65; 44,81</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 22,57</t>
+          <t>-2,82; 23,35</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 1,47</t>
+          <t>-19,67; 2,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15,21; 62,4</t>
+          <t>15,42; 56,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP15-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP15-Habitat-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,82</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-1,09</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-5,44</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,62</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,52</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,4</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>-1,93</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-0,45</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 7,39</t>
+          <t>-4,33; 11,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 2,88</t>
+          <t>-9,41; 4,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 7,28</t>
+          <t>-7,83; 8,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 11,13</t>
+          <t>-9,57; 6,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 5,33</t>
+          <t>-14,14; 2,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 10,85</t>
+          <t>-10,5; 6,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 6,99</t>
+          <t>-4,14; 6,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 1,55</t>
+          <t>-9,24; 1,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 6,53</t>
+          <t>-5,65; 5,45</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18,81%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-12,84%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-4,61%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-22,99%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-6,86%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18,81%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-12,84%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>-8,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-1,48%</t>
+          <t>-2,15%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,57; 40,39</t>
+          <t>-20,19; 73,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,75; 16,02</t>
+          <t>-42,22; 31,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-35,7; 38,1</t>
+          <t>-36,78; 58,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 77,91</t>
+          <t>-35,21; 35,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,39; 37,57</t>
+          <t>-49,23; 17,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,67; 70,11</t>
+          <t>-37,13; 33,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 37,4</t>
+          <t>-17,91; 38,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,67; 8,51</t>
+          <t>-39,69; 8,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-23,93; 36,29</t>
+          <t>-24,51; 29,56</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,13</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,39</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-1,23</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,74</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,46</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,62</t>
+          <t>-1,74</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>1,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 4,73</t>
+          <t>-7,49; 4,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 5,64</t>
+          <t>-7,1; 4,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 11,24</t>
+          <t>-1,95; 11,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 4,31</t>
+          <t>-8,55; 4,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 4,88</t>
+          <t>-7,06; 5,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 12,51</t>
+          <t>-8,78; 4,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 3,14</t>
+          <t>-5,65; 2,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 3,05</t>
+          <t>-5,2; 3,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 8,89</t>
+          <t>-3,09; 6,72</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-7,49%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-5,81%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22,56%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-5,75%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-3,45%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-7,49%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-5,81%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>-8,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,31; 25,02</t>
+          <t>-33,41; 28,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 32,94</t>
+          <t>-30,41; 24,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,34; 60,28</t>
+          <t>-9,38; 68,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,42; 26,36</t>
+          <t>-32,42; 26,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,6; 29,7</t>
+          <t>-27,39; 31,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 72,34</t>
+          <t>-36,12; 26,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,85; 17,3</t>
+          <t>-25,44; 15,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 16,3</t>
+          <t>-23,02; 18,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 50,37</t>
+          <t>-13,96; 35,86</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-6,79</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,63</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>2,96</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,56</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>23,16</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,5</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-6,79</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>14,46</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15,11</t>
+          <t>10,91</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 9,62</t>
+          <t>-10,16; 5,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 6,62</t>
+          <t>-14,69; 0,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,78; 46,42</t>
+          <t>-1,26; 15,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 6,62</t>
+          <t>-4,66; 10,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 0,96</t>
+          <t>-7,55; 6,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 16,27</t>
+          <t>6,67; 23,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 6,27</t>
+          <t>-4,05; 5,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 1,35</t>
+          <t>-8,64; 1,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 29,3</t>
+          <t>5,0; 17,59</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-6,38%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-28,91%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>32,52%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>16,19%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-3,05%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>126,83%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-6,38%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-28,91%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 63,67</t>
+          <t>-35,24; 31,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,9; 46,51</t>
+          <t>-50,84; 3,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52,02; 331,02</t>
+          <t>-4,5; 82,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,05; 34,73</t>
+          <t>-20,37; 68,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,75; 6,34</t>
+          <t>-34,78; 43,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 80,79</t>
+          <t>30,79; 165,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 33,9</t>
+          <t>-17,31; 33,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-38,7; 6,54</t>
+          <t>-37,0; 5,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32,83; 150,94</t>
+          <t>21,49; 93,2</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-4,02</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,07</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>7,6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3,54</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5,93</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,15</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-4,02</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>2,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 14,32</t>
+          <t>-2,66; 10,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 9,23</t>
+          <t>-9,39; 2,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 12,14</t>
+          <t>-5,95; 6,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 10,8</t>
+          <t>1,18; 13,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 2,16</t>
+          <t>-2,23; 9,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 6,98</t>
+          <t>-0,32; 11,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 10,48</t>
+          <t>1,24; 10,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 4,37</t>
+          <t>-4,13; 4,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 7,8</t>
+          <t>-1,87; 6,95</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>22,22%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-21,55%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-0,37%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>61,98%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>28,86%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>48,32%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>22,22%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-21,55%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-0,12%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,41; 154,03</t>
+          <t>-11,47; 73,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 103,95</t>
+          <t>-45,76; 16,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 126,33</t>
+          <t>-27,83; 44,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 70,55</t>
+          <t>3,62; 140,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,81; 14,29</t>
+          <t>-15,9; 103,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,1; 45,36</t>
+          <t>-3,86; 110,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,5; 77,33</t>
+          <t>6,68; 74,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 33,48</t>
+          <t>-24,03; 30,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 59,13</t>
+          <t>-10,95; 52,48</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-3,36</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3,64</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2,36</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,3</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>8,45</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-3,36</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,02</t>
+          <t>4,37</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,11</t>
+          <t>4,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 5,9</t>
+          <t>-2,38; 4,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 2,64</t>
+          <t>-6,64; -0,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,24; 18,79</t>
+          <t>-0,82; 7,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,61</t>
+          <t>-0,75; 6,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,66; -0,1</t>
+          <t>-3,84; 2,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 8,13</t>
+          <t>0,88; 8,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,15</t>
+          <t>-0,93; 4,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,4</t>
+          <t>-4,4; 0,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,17; 10,59</t>
+          <t>1,44; 6,84</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-16,89%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>18,3%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>12,84%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-1,65%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>45,94%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-16,89%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 34,41</t>
+          <t>-10,96; 23,94</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 15,96</t>
+          <t>-30,26; -1,01</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16,31; 104,05</t>
+          <t>-3,76; 38,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 25,21</t>
+          <t>-3,71; 35,93</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-30,25; -0,48</t>
+          <t>-19,16; 16,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,65; 44,81</t>
+          <t>4,36; 49,64</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 23,35</t>
+          <t>-4,57; 23,55</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 2,2</t>
+          <t>-21,61; 2,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15,42; 56,87</t>
+          <t>7,06; 38,42</t>
         </is>
       </c>
     </row>
